--- a/rules/CORE-000706/negative/01/data/unit-test-coreid-FB0906-negative.xlsx
+++ b/rules/CORE-000706/negative/01/data/unit-test-coreid-FB0906-negative.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Validation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ae.xpt" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="cm.xpt" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="mh.xpt" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ae.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cm.xpt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mh.xpt" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43,7 +43,7 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +72,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -117,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -157,6 +163,9 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -625,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,6 +666,444 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Error value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AELLT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Upset stomach</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AELLTCD</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10046318</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AELLT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Headache</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AELLTCD</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10019211</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AELLT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Headache</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AELLTCD</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>10019212</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AELLT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Headache</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AELLTCD</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10019212</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AELLT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AELLTCD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>10019211</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AELLT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Hypertension</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AELLTCD</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>10020772</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AELLT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Hypertension</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AELLTCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AELLT</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Cardiac arrest</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AELLTCD</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>10046318</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1770,12 @@
           <t>UPSET STOMACH</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>Upset stomach</t>
         </is>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="17" t="n">
         <v>10046318</v>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -1464,12 +1911,12 @@
           <t>HEADACHE</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>Headache</t>
         </is>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H6" s="17" t="n">
         <v>10019211</v>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -1605,12 +2052,12 @@
           <t>HEADACHE</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>Headache</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>10019212</t>
         </is>
@@ -1748,12 +2195,12 @@
           <t>HEADACHE</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>Headache</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>10019212</t>
         </is>
@@ -1891,8 +2338,8 @@
           <t>HEADACHE</t>
         </is>
       </c>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n">
+      <c r="G9" s="17" t="n"/>
+      <c r="H9" s="17" t="n">
         <v>10019211</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
@@ -2028,12 +2475,12 @@
           <t>HYPERTENSION</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>Hypertension</t>
         </is>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="H10" s="17" t="n">
         <v>10020772</v>
       </c>
       <c r="I10" s="10" t="inlineStr">
@@ -2169,12 +2616,12 @@
           <t>HYPERTENSION</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Hypertension</t>
         </is>
       </c>
-      <c r="H11" s="11" t="n"/>
+      <c r="H11" s="17" t="n"/>
       <c r="I11" s="10" t="inlineStr">
         <is>
           <t>Hypertension</t>
@@ -2449,12 +2896,12 @@
           <t>CARDIAC ARREST</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>Cardiac arrest</t>
         </is>
       </c>
-      <c r="H13" s="11" t="n">
+      <c r="H13" s="17" t="n">
         <v>10046318</v>
       </c>
       <c r="I13" s="10" t="inlineStr">
@@ -11093,7 +11540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11124,25 +11571,15 @@
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
-          <t>MHLLT</t>
+          <t>MHEVDTYP</t>
         </is>
       </c>
       <c r="G1" s="5" t="inlineStr">
         <is>
-          <t>MHLLTCD</t>
+          <t>MHSTDTC</t>
         </is>
       </c>
       <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>MHEVDTYP</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>MHSTDTC</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>MHSTDY</t>
         </is>
@@ -11176,25 +11613,15 @@
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>Lowest Level Term</t>
+          <t>Medical History Event Date Type</t>
         </is>
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>Lowest Level Term Code</t>
+          <t>Start Date/Time of Medical History Event</t>
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>Medical History Event Date Type</t>
-        </is>
-      </c>
-      <c r="I2" s="8" t="inlineStr">
-        <is>
-          <t>Start Date/Time of Medical History Event</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>Study Day of Start of Observation</t>
         </is>
@@ -11233,20 +11660,10 @@
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>Num</t>
+          <t>Char</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
@@ -11269,18 +11686,12 @@
         <v>19</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="I4" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" s="8" t="n">
         <v>8</v>
       </c>
     </row>
@@ -11308,27 +11719,17 @@
           <t>ALZHEIMER'S DISEASE</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>10001896</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>SYMPTOM ONSET</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>2004-05-28</t>
         </is>
       </c>
-      <c r="J5" s="10" t="n">
+      <c r="H5" s="10" t="n">
         <v>-3108</v>
       </c>
     </row>
@@ -11356,27 +11757,17 @@
           <t>ALZHEIMER'S DISEASE</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>Alzheimer disease</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>10001896</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>SYMPTOM ONSET</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>2010-03-19</t>
         </is>
       </c>
-      <c r="J6" s="10" t="n">
+      <c r="H6" s="10" t="n">
         <v>-972</v>
       </c>
     </row>
@@ -11404,27 +11795,17 @@
           <t>ALZHEIMER'S DISEASE</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>10001897</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>SYMPTOM ONSET</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>2007-02-09</t>
         </is>
       </c>
-      <c r="J7" s="10" t="n">
+      <c r="H7" s="10" t="n">
         <v>-2393</v>
       </c>
     </row>
@@ -11452,23 +11833,17 @@
           <t>ALZHEIMER'S DISEASE</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>10001897</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>SYMPTOM ONSET</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>2010-11-05</t>
         </is>
       </c>
-      <c r="J8" s="10" t="n">
+      <c r="H8" s="10" t="n">
         <v>-1068</v>
       </c>
     </row>
@@ -11496,23 +11871,17 @@
           <t>ALZHEIMER'S DISEASE</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>Alzheimer disease</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>SYMPTOM ONSET</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>2006-08-20</t>
         </is>
       </c>
-      <c r="J9" s="10" t="n">
+      <c r="H9" s="10" t="n">
         <v>-2360</v>
       </c>
     </row>
@@ -11540,23 +11909,17 @@
           <t>ALZHEIMER'S DISEASE</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>10001898</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>SYMPTOM ONSET</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>2010-11-05</t>
         </is>
       </c>
-      <c r="J10" s="10" t="n">
+      <c r="H10" s="10" t="n">
         <v>-1068</v>
       </c>
     </row>
